--- a/data/xlsx/dte--it-support-technique-and-mobile-phone-servicing.xlsx
+++ b/data/xlsx/dte--it-support-technique-and-mobile-phone-servicing.xlsx
@@ -648,7 +648,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>8</v>
       </c>
@@ -670,7 +672,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>6</v>
       </c>
@@ -692,7 +696,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>6</v>
       </c>
@@ -715,7 +721,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>10</v>
       </c>
@@ -738,7 +746,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -760,7 +770,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>9</v>
       </c>
@@ -786,7 +798,9 @@
       <c r="C22" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>8</v>
       </c>
@@ -812,7 +826,9 @@
       <c r="C23" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -838,7 +854,9 @@
       <c r="C24" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>4</v>
       </c>
@@ -860,7 +878,9 @@
       <c r="C25" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>3</v>
       </c>
@@ -882,7 +902,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>7</v>
       </c>
@@ -904,7 +926,9 @@
       <c r="C27" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>8</v>
       </c>
@@ -926,7 +950,9 @@
       <c r="C28" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>8</v>
       </c>
@@ -948,7 +974,9 @@
       <c r="C29" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>7</v>
       </c>
@@ -970,7 +998,9 @@
       <c r="C30" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>8</v>
       </c>
@@ -992,7 +1022,9 @@
       <c r="C31" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>7</v>
       </c>
@@ -1014,7 +1046,9 @@
       <c r="C32" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>6</v>
       </c>
@@ -1036,7 +1070,9 @@
       <c r="C33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>6</v>
       </c>
@@ -1058,7 +1094,9 @@
       <c r="C34" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>5</v>
       </c>
@@ -1080,7 +1118,9 @@
       <c r="C35" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>4</v>
       </c>
@@ -1102,7 +1142,9 @@
       <c r="C36" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>3</v>
       </c>
@@ -1124,7 +1166,9 @@
       <c r="C37" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>3</v>
       </c>
@@ -1146,7 +1190,9 @@
       <c r="C38" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>3</v>
       </c>
@@ -1168,7 +1214,9 @@
       <c r="C39" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D39" s="9" t="n"/>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="9" t="n">
         <v>4</v>
       </c>
@@ -1190,7 +1238,9 @@
       <c r="C40" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="D40" s="9" t="n"/>
+      <c r="D40" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="9" t="n">
         <v>8</v>
       </c>
@@ -1212,7 +1262,9 @@
       <c r="C41" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D41" s="9" t="n"/>
+      <c r="D41" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="9" t="n">
         <v>7</v>
       </c>
